--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260807.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>889,349</t>
+          <t>104,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>146,482</t>
+          <t>1,388,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,388,000</t>
+          <t>146,482</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>104,000</t>
+          <t>889,349</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,343,000</t>
+          <t>1,901,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,901,000</t>
+          <t>3,343,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>10,997,121</t>
+          <t>604,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>7,437,249</t>
+          <t>10,997,121</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>604,000</t>
+          <t>7,437,249</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>188,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>5,145,956</t>
+          <t>805,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>834,000</t>
+          <t>404,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>404,000</t>
+          <t>834,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>805,000</t>
+          <t>5,145,956</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>301,000</t>
+          <t>1,618,400</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1,618,400</t>
+          <t>301,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>236,000</t>
+          <t>119,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>516,000</t>
+          <t>236,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>119,000</t>
+          <t>516,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>264,000</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>705,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>705,000</t>
+          <t>264,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
